--- a/translation/review/000scriptAKYO_0036T.xlsx
+++ b/translation/review/000scriptAKYO_0036T.xlsx
@@ -34,13 +34,13 @@
     <t>I have no such intention, but is now the time to be quarreling!?</t>
   </si>
   <si>
-    <t>No tengo esa intención, ¡¿pero es ahora el momento de pelear?!</t>
+    <t>No tengo esa intención, ¡¿pero es ahora el＿momento de pelear?!</t>
   </si>
   <si>
     <t>You have to give it straight to that girl. you know?</t>
   </si>
   <si>
-    <t>Tienes que decírselo directamente a esa chica, ¿sabes?</t>
+    <t>Tienes que decírselo directamente a esa chica,＿¿sabes?</t>
   </si>
   <si>
     <t>That - is - why I'm asking you to cool down your head!</t>
@@ -52,7 +52,7 @@
     <t>That - is - why I'm telling you not to butt in this conversation!</t>
   </si>
   <si>
-    <t>¡Por - eso - te digo que no te metas en esta conversación!</t>
+    <t>¡Por - eso - te digo que no te metas en esta＿conversación!</t>
   </si>
   <si>
     <t>Well, hold on. Listen...</t>
@@ -70,7 +70,7 @@
     <t>Anyway, you're quite peculiar as well.</t>
   </si>
   <si>
-    <t>De todos modos, tú también eres bastante peculiar.</t>
+    <t>De todos modos, tú también eres bastante＿peculiar.</t>
   </si>
   <si>
     <t>Me?!</t>
@@ -82,7 +82,7 @@
     <t>Do you even know the meaning of teamwork?</t>
   </si>
   <si>
-    <t>¿Siquiera sabes el significado de trabajo en equipo?</t>
+    <t>¿Siquiera sabes el significado de trabajo en＿equipo?</t>
   </si>
   <si>
     <t>Don't take me for a fool! I know that much!</t>
@@ -94,7 +94,7 @@
     <t>Is that the attitude of someone who understands teamwork? You're just disrupting it.</t>
   </si>
   <si>
-    <t>¿Esa es la actitud de alguien que entiende el trabajo en equipo? Solo lo estás perturbando.</t>
+    <t>¿Esa es la actitud de alguien que entiende el＿trabajo en equipo? Solo lo estás perturbando.</t>
   </si>
   <si>
     <t>I don't want to hear that from you!</t>
@@ -106,7 +106,7 @@
     <t>I'm personally teaching you what teamwork is, so I'd like some gratitude.</t>
   </si>
   <si>
-    <t>Te estoy enseñando personalmente qué es el trabajo en equipo, así que me gustaría algo de gratitud.</t>
+    <t>Te estoy enseñando personalmente qué es el＿trabajo en equipo, así que me gustaría algo de＿gratitud.</t>
   </si>
   <si>
     <t>Y-You...</t>
@@ -133,7 +133,7 @@
     <t>Right now, no one else but you is disrupting our teamwork.</t>
   </si>
   <si>
-    <t>Ahora mismo, nadie más que tú está perturbando nuestro trabajo en equipo.</t>
+    <t>Ahora mismo, nadie más que tú está＿perturbando nuestro trabajo en equipo.</t>
   </si>
   <si>
     <t>...I have no idea what you're talking about.</t>
@@ -145,13 +145,13 @@
     <t>I'll explain it so that even YOU can understand...</t>
   </si>
   <si>
-    <t>Te lo explicaré para que incluso TÚ puedas entenderlo...</t>
+    <t>Te lo explicaré para que incluso TÚ puedas＿entenderlo...</t>
   </si>
   <si>
     <t>The kanji "person" is written in such a way, where one person supports the other.</t>
   </si>
   <si>
-    <t>El kanji «persona» se escribe de tal manera que una persona sostiene a la otra.</t>
+    <t>El kanji «persona» se escribe de tal manera que＿una persona sostiene a la otra.</t>
   </si>
   <si>
     <t>That's straight from some drama!</t>
@@ -175,7 +175,7 @@
     <t>This is the reason why our teamwork is being disrupted.</t>
   </si>
   <si>
-    <t>Esta es la razón por la que nuestro trabajo en equipo está siendo perturbado.</t>
+    <t>Esta es la razón por la que nuestro trabajo en＿equipo está siendo perturbado.</t>
   </si>
   <si>
     <t>Why can't you just understand that?</t>
@@ -199,13 +199,13 @@
     <t>She looks so proud, but this is such a cliché line.</t>
   </si>
   <si>
-    <t>Se ve tan orgullosa, pero esta es una línea tan cliché.</t>
+    <t>Se ve tan orgullosa, pero esta es una línea tan＿cliché.</t>
   </si>
   <si>
     <t>Your moves in "Siscaly" are so poor that you instantly die!</t>
   </si>
   <si>
-    <t>¡Tus movimientos en «Siscaly» son tan pobres que mueres al instante!</t>
+    <t>¡Tus movimientos en «Siscaly» son tan pobres＿que mueres al instante!</t>
   </si>
   <si>
     <t>There's no link between those two things!</t>
@@ -217,7 +217,7 @@
     <t>Well, if you were to watch me play about a million times, perhaps you would become a slightly better human being.</t>
   </si>
   <si>
-    <t>Bueno, si me vieras jugar como un millón de veces, quizás te volverías un ser humano un poco mejor.</t>
+    <t>Bueno, si me vieras jugar como un millón de＿veces, quizás te volverías un ser humano un＿poco mejor.</t>
   </si>
   <si>
     <t>Are you a Thief of Time?!</t>
@@ -235,7 +235,7 @@
     <t>You're taking precious time from my preparations for exams! Can you get to the point?</t>
   </si>
   <si>
-    <t>¡Estás quitando tiempo precioso de mis preparativos para los exámenes! ¿Puedes ir al grano?</t>
+    <t>¡Estás quitando tiempo precioso de mis＿preparativos para los exámenes! ¿Puedes ir al＿grano?</t>
   </si>
   <si>
     <t>What were we talking about anyway?</t>
@@ -259,7 +259,7 @@
     <t>Ah, that's right. Also, upload my gameplay videos to Nico Douga.</t>
   </si>
   <si>
-    <t>Ah, cierto. Además, sube mis videos de juego a Nico Douga.</t>
+    <t>Ah, cierto. Además, sube mis videos de juego a＿Nico Douga.</t>
   </si>
   <si>
     <t>Eh? What did you just say?</t>
@@ -295,7 +295,7 @@
     <t>By the way, if the number of views doesn't increase... You know what'll happen...</t>
   </si>
   <si>
-    <t>Por cierto, si el número de visitas no aumenta... Sabes lo que pasará...</t>
+    <t>Por cierto, si el número de visitas no aumenta...＿Sabes lo que pasará...</t>
   </si>
   <si>
     <t>...I will do my best.</t>
@@ -307,7 +307,7 @@
     <t>Anyway, if you don't know what teamwork is, then there is no use helping one another.</t>
   </si>
   <si>
-    <t>De todos modos, si no sabes qué es el trabajo en equipo, entonces no sirve de nada ayudarse mutuamente.</t>
+    <t>De todos modos, si no sabes qué es el trabajo＿en equipo, entonces no sirve de nada ayudarse＿mutuamente.</t>
   </si>
   <si>
     <t>............</t>
@@ -334,13 +334,13 @@
     <t>Really, I'm tired of having such a stupid elder brother...</t>
   </si>
   <si>
-    <t>De verdad, estoy harta de tener un hermano mayor tan estúpido...</t>
+    <t>De verdad, estoy harta de tener un hermano＿mayor tan estúpido...</t>
   </si>
   <si>
     <t>Seriously... I'm the one who is tired of having such a horrible little sister...</t>
   </si>
   <si>
-    <t>En serio... Soy yo quien está harto de tener una hermanita tan horrible...</t>
+    <t>En serio... Soy yo quien está harto de tener una＿hermanita tan horrible...</t>
   </si>
 </sst>
 </file>
